--- a/逆合成/hiwo任务11-48-03.xlsx
+++ b/逆合成/hiwo任务11-48-03.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.11.80\立项组\立项组\李伟龙\逆合成\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775" firstSheet="2" activeTab="7"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="任务参数配置" sheetId="1" r:id="rId1"/>
@@ -707,7 +712,7 @@
     <t>移液+磁力搅拌+淬灭液+加稀释液+正压过滤(带中转板)</t>
   </si>
   <si>
-    <t>FY96-B01</t>
+    <t>B01-FY96</t>
   </si>
   <si>
     <t>℃</t>
